--- a/output/tables/B25_ice_sheet_summary_tables.xlsx
+++ b/output/tables/B25_ice_sheet_summary_tables.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="621">
   <si>
     <t>Year</t>
   </si>
@@ -639,13 +639,13 @@
     <t>192 ± 74</t>
   </si>
   <si>
-    <t>336 ± 94</t>
-  </si>
-  <si>
-    <t>291 ± 114</t>
-  </si>
-  <si>
-    <t>368 ± 108</t>
+    <t>−310 ± 94</t>
+  </si>
+  <si>
+    <t>−265 ± 108</t>
+  </si>
+  <si>
+    <t>17 ± 85</t>
   </si>
   <si>
     <t>−328 ± 145</t>
@@ -675,13 +675,13 @@
     <t>227 ± 112</t>
   </si>
   <si>
-    <t>347 ± 149</t>
-  </si>
-  <si>
-    <t>330 ± 182</t>
-  </si>
-  <si>
-    <t>419 ± 155</t>
+    <t>−308 ± 150</t>
+  </si>
+  <si>
+    <t>−287 ± 175</t>
+  </si>
+  <si>
+    <t>34 ± 126</t>
   </si>
   <si>
     <t>−366 ± 224</t>
@@ -711,13 +711,13 @@
     <t>275 ± 165</t>
   </si>
   <si>
-    <t>399 ± 230</t>
-  </si>
-  <si>
-    <t>359 ± 235</t>
-  </si>
-  <si>
-    <t>479 ± 218</t>
+    <t>−334 ± 231</t>
+  </si>
+  <si>
+    <t>−292 ± 224</t>
+  </si>
+  <si>
+    <t>72 ± 193</t>
   </si>
   <si>
     <t>−658 ± 220</t>
@@ -747,13 +747,13 @@
     <t>463 ± 266</t>
   </si>
   <si>
-    <t>689 ± 225</t>
-  </si>
-  <si>
-    <t>624 ± 295</t>
-  </si>
-  <si>
-    <t>822 ± 312</t>
+    <t>−626 ± 224</t>
+  </si>
+  <si>
+    <t>−552 ± 272</t>
+  </si>
+  <si>
+    <t>103 ± 262</t>
   </si>
   <si>
     <t>−671 ± 350</t>
@@ -783,13 +783,13 @@
     <t>710 ± 397</t>
   </si>
   <si>
-    <t>730 ± 361</t>
-  </si>
-  <si>
-    <t>744 ± 432</t>
-  </si>
-  <si>
-    <t>1083 ± 453</t>
+    <t>−612 ± 363</t>
+  </si>
+  <si>
+    <t>−511 ± 397</t>
+  </si>
+  <si>
+    <t>338 ± 388</t>
   </si>
   <si>
     <t>−768 ± 514</t>
@@ -819,13 +819,13 @@
     <t>783 ± 556</t>
   </si>
   <si>
-    <t>883 ± 546</t>
-  </si>
-  <si>
-    <t>879 ± 620</t>
-  </si>
-  <si>
-    <t>1067 ± 638</t>
+    <t>−654 ± 547</t>
+  </si>
+  <si>
+    <t>−448 ± 549</t>
+  </si>
+  <si>
+    <t>499 ± 547</t>
   </si>
   <si>
     <t>−950 ± 374</t>
@@ -855,13 +855,13 @@
     <t>800 ± 513</t>
   </si>
   <si>
-    <t>1016 ± 384</t>
-  </si>
-  <si>
-    <t>997 ± 460</t>
-  </si>
-  <si>
-    <t>1306 ± 582</t>
+    <t>−884 ± 385</t>
+  </si>
+  <si>
+    <t>−782 ± 424</t>
+  </si>
+  <si>
+    <t>294 ± 497</t>
   </si>
   <si>
     <t>−999 ± 530</t>
@@ -891,13 +891,13 @@
     <t>1012 ± 611</t>
   </si>
   <si>
-    <t>1107 ± 551</t>
-  </si>
-  <si>
-    <t>1175 ± 637</t>
-  </si>
-  <si>
-    <t>1573 ± 685</t>
+    <t>−890 ± 547</t>
+  </si>
+  <si>
+    <t>−690 ± 559</t>
+  </si>
+  <si>
+    <t>452 ± 595</t>
   </si>
   <si>
     <t>−1138 ± 775</t>
@@ -927,13 +927,13 @@
     <t>1386 ± 914</t>
   </si>
   <si>
-    <t>1387 ± 858</t>
-  </si>
-  <si>
-    <t>1368 ± 841</t>
-  </si>
-  <si>
-    <t>1970 ± 1013</t>
+    <t>−888 ± 862</t>
+  </si>
+  <si>
+    <t>−553 ± 742</t>
+  </si>
+  <si>
+    <t>802 ± 890</t>
   </si>
   <si>
     <t>−314</t>
@@ -960,13 +960,13 @@
     <t>188</t>
   </si>
   <si>
-    <t>328</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>362</t>
+    <t>−302</t>
+  </si>
+  <si>
+    <t>−249</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>−296</t>
@@ -996,13 +996,13 @@
     <t>202</t>
   </si>
   <si>
-    <t>318</t>
-  </si>
-  <si>
-    <t>293</t>
-  </si>
-  <si>
-    <t>393</t>
+    <t>−283</t>
+  </si>
+  <si>
+    <t>−253</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
   <si>
     <t>−317</t>
@@ -1026,13 +1026,13 @@
     <t>256</t>
   </si>
   <si>
-    <t>353</t>
-  </si>
-  <si>
-    <t>309</t>
-  </si>
-  <si>
-    <t>444</t>
+    <t>−295</t>
+  </si>
+  <si>
+    <t>−251</t>
+  </si>
+  <si>
+    <t>67</t>
   </si>
   <si>
     <t>−656</t>
@@ -1056,13 +1056,13 @@
     <t>384</t>
   </si>
   <si>
-    <t>683</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>767</t>
+    <t>−619</t>
+  </si>
+  <si>
+    <t>−513</t>
+  </si>
+  <si>
+    <t>57</t>
   </si>
   <si>
     <t>−617</t>
@@ -1092,13 +1092,13 @@
     <t>647</t>
   </si>
   <si>
-    <t>673</t>
-  </si>
-  <si>
-    <t>655</t>
-  </si>
-  <si>
-    <t>1023</t>
+    <t>−569</t>
+  </si>
+  <si>
+    <t>−479</t>
+  </si>
+  <si>
+    <t>284</t>
   </si>
   <si>
     <t>−685</t>
@@ -1116,22 +1116,16 @@
     <t>979</t>
   </si>
   <si>
-    <t>284</t>
-  </si>
-  <si>
     <t>34</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>781</t>
-  </si>
-  <si>
-    <t>713</t>
-  </si>
-  <si>
-    <t>945</t>
+    <t>−594</t>
+  </si>
+  <si>
+    <t>−458</t>
+  </si>
+  <si>
+    <t>397</t>
   </si>
   <si>
     <t>−980</t>
@@ -1161,10 +1155,13 @@
     <t>677</t>
   </si>
   <si>
-    <t>940</t>
-  </si>
-  <si>
-    <t>1219</t>
+    <t>−893</t>
+  </si>
+  <si>
+    <t>−726</t>
+  </si>
+  <si>
+    <t>216</t>
   </si>
   <si>
     <t>−923</t>
@@ -1194,13 +1191,13 @@
     <t>908</t>
   </si>
   <si>
-    <t>1032</t>
-  </si>
-  <si>
-    <t>1054</t>
-  </si>
-  <si>
-    <t>1478</t>
+    <t>−825</t>
+  </si>
+  <si>
+    <t>−653</t>
+  </si>
+  <si>
+    <t>365</t>
   </si>
   <si>
     <t>−1000</t>
@@ -1227,13 +1224,10 @@
     <t>1220</t>
   </si>
   <si>
-    <t>1223</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>1826</t>
+    <t>−811</t>
+  </si>
+  <si>
+    <t>−574</t>
   </si>
   <si>
     <t>−477–−213</t>
@@ -1263,13 +1257,13 @@
     <t>101–315</t>
   </si>
   <si>
-    <t>214–491</t>
-  </si>
-  <si>
-    <t>178–452</t>
-  </si>
-  <si>
-    <t>206–573</t>
+    <t>−444–−174</t>
+  </si>
+  <si>
+    <t>−347–−140</t>
+  </si>
+  <si>
+    <t>−114–154</t>
   </si>
   <si>
     <t>−449–−179</t>
@@ -1299,13 +1293,13 @@
     <t>123–330</t>
   </si>
   <si>
-    <t>201–585</t>
-  </si>
-  <si>
-    <t>186–587</t>
-  </si>
-  <si>
-    <t>238–766</t>
+    <t>−455–−117</t>
+  </si>
+  <si>
+    <t>−541–−120</t>
+  </si>
+  <si>
+    <t>−124–198</t>
   </si>
   <si>
     <t>−496–−175</t>
@@ -1335,13 +1329,13 @@
     <t>107–382</t>
   </si>
   <si>
-    <t>206–740</t>
-  </si>
-  <si>
-    <t>189–691</t>
-  </si>
-  <si>
-    <t>242–968</t>
+    <t>−510–−91</t>
+  </si>
+  <si>
+    <t>−596–−90</t>
+  </si>
+  <si>
+    <t>−157–293</t>
   </si>
   <si>
     <t>−1010–−419</t>
@@ -1371,13 +1365,13 @@
     <t>159–946</t>
   </si>
   <si>
-    <t>422–1015</t>
-  </si>
-  <si>
-    <t>373–980</t>
-  </si>
-  <si>
-    <t>389–1393</t>
+    <t>−941–−324</t>
+  </si>
+  <si>
+    <t>−742–−270</t>
+  </si>
+  <si>
+    <t>−247–559</t>
   </si>
   <si>
     <t>−850–−356</t>
@@ -1407,13 +1401,13 @@
     <t>254–1400</t>
   </si>
   <si>
-    <t>417–1252</t>
-  </si>
-  <si>
-    <t>374–1634</t>
-  </si>
-  <si>
-    <t>473–1889</t>
+    <t>−871–−210</t>
+  </si>
+  <si>
+    <t>−872–−78</t>
+  </si>
+  <si>
+    <t>−185–939</t>
   </si>
   <si>
     <t>−998–−413</t>
@@ -1443,13 +1437,13 @@
     <t>153–1420</t>
   </si>
   <si>
-    <t>431–1761</t>
-  </si>
-  <si>
-    <t>358–2367</t>
-  </si>
-  <si>
-    <t>317–2220</t>
+    <t>−1033–−74</t>
+  </si>
+  <si>
+    <t>−884–193</t>
+  </si>
+  <si>
+    <t>−214–1271</t>
   </si>
   <si>
     <t>−1520–−526</t>
@@ -1479,13 +1473,13 @@
     <t>202–1490</t>
   </si>
   <si>
-    <t>541–1538</t>
-  </si>
-  <si>
-    <t>520–1625</t>
-  </si>
-  <si>
-    <t>507–2292</t>
+    <t>−1382–−358</t>
+  </si>
+  <si>
+    <t>−1346–−292</t>
+  </si>
+  <si>
+    <t>−363–1131</t>
   </si>
   <si>
     <t>−1360–−450</t>
@@ -1515,13 +1509,13 @@
     <t>312–2080</t>
   </si>
   <si>
-    <t>546–1957</t>
-  </si>
-  <si>
-    <t>549–2450</t>
-  </si>
-  <si>
-    <t>652–2770</t>
+    <t>−1393–−244</t>
+  </si>
+  <si>
+    <t>−1241–−9</t>
+  </si>
+  <si>
+    <t>−336–1379</t>
   </si>
   <si>
     <t>−2390–−524</t>
@@ -1551,13 +1545,13 @@
     <t>405–2370</t>
   </si>
   <si>
-    <t>574–3180</t>
-  </si>
-  <si>
-    <t>504–3363</t>
-  </si>
-  <si>
-    <t>705–3614</t>
+    <t>−1973–90</t>
+  </si>
+  <si>
+    <t>−1221–345</t>
+  </si>
+  <si>
+    <t>−300–2011</t>
   </si>
   <si>
     <t>−403–−239</t>
@@ -1587,13 +1581,13 @@
     <t>124–254</t>
   </si>
   <si>
-    <t>250–416</t>
-  </si>
-  <si>
-    <t>223–342</t>
-  </si>
-  <si>
-    <t>272–453</t>
+    <t>−392–−227</t>
+  </si>
+  <si>
+    <t>−313–−206</t>
+  </si>
+  <si>
+    <t>−55–87</t>
   </si>
   <si>
     <t>−408–−230</t>
@@ -1623,13 +1617,13 @@
     <t>145–298</t>
   </si>
   <si>
-    <t>244–428</t>
-  </si>
-  <si>
-    <t>229–385</t>
-  </si>
-  <si>
-    <t>302–507</t>
+    <t>−395–−212</t>
+  </si>
+  <si>
+    <t>−339–−202</t>
+  </si>
+  <si>
+    <t>−48–112</t>
   </si>
   <si>
     <t>−449–−237</t>
@@ -1659,13 +1653,13 @@
     <t>163–348</t>
   </si>
   <si>
-    <t>257–483</t>
-  </si>
-  <si>
-    <t>235–411</t>
-  </si>
-  <si>
-    <t>323–573</t>
+    <t>−425–−205</t>
+  </si>
+  <si>
+    <t>−342–−192</t>
+  </si>
+  <si>
+    <t>−44–174</t>
   </si>
   <si>
     <t>−796–−476</t>
@@ -1695,13 +1689,13 @@
     <t>219–725</t>
   </si>
   <si>
-    <t>507–826</t>
-  </si>
-  <si>
-    <t>457–736</t>
-  </si>
-  <si>
-    <t>540–1120</t>
+    <t>−769–−448</t>
+  </si>
+  <si>
+    <t>−654–−413</t>
+  </si>
+  <si>
+    <t>−132–355</t>
   </si>
   <si>
     <t>−788–−467</t>
@@ -1731,13 +1725,13 @@
     <t>355–1060</t>
   </si>
   <si>
-    <t>510–848</t>
-  </si>
-  <si>
-    <t>476–886</t>
-  </si>
-  <si>
-    <t>678–1465</t>
+    <t>−747–−409</t>
+  </si>
+  <si>
+    <t>−641–−305</t>
+  </si>
+  <si>
+    <t>1–667</t>
   </si>
   <si>
     <t>−909–−486</t>
@@ -1767,13 +1761,13 @@
     <t>360–1210</t>
   </si>
   <si>
-    <t>553–1032</t>
-  </si>
-  <si>
-    <t>487–1108</t>
-  </si>
-  <si>
-    <t>546–1544</t>
+    <t>−843–−362</t>
+  </si>
+  <si>
+    <t>−664–−179</t>
+  </si>
+  <si>
+    <t>97–911</t>
   </si>
   <si>
     <t>−1140–−636</t>
@@ -1803,13 +1797,13 @@
     <t>339–1290</t>
   </si>
   <si>
-    <t>705–1206</t>
-  </si>
-  <si>
-    <t>661–1237</t>
-  </si>
-  <si>
-    <t>778–1840</t>
+    <t>−1096–−574</t>
+  </si>
+  <si>
+    <t>−992–−515</t>
+  </si>
+  <si>
+    <t>−157–737</t>
   </si>
   <si>
     <t>−1240–−636</t>
@@ -1839,13 +1833,13 @@
     <t>466–1550</t>
   </si>
   <si>
-    <t>720–1356</t>
-  </si>
-  <si>
-    <t>711–1497</t>
-  </si>
-  <si>
-    <t>957–2160</t>
+    <t>−1156–−525</t>
+  </si>
+  <si>
+    <t>−958–−336</t>
+  </si>
+  <si>
+    <t>−65–955</t>
   </si>
   <si>
     <t>−1420–−651</t>
@@ -1875,13 +1869,13 @@
     <t>622–2060</t>
   </si>
   <si>
-    <t>800–1707</t>
-  </si>
-  <si>
-    <t>759–1809</t>
-  </si>
-  <si>
-    <t>1109–2723</t>
+    <t>−1274–−377</t>
+  </si>
+  <si>
+    <t>−948–−124</t>
+  </si>
+  <si>
+    <t>80–1447</t>
   </si>
   <si>
     <t>Projected ice-sheet contributions to global mean sea level</t>
@@ -2270,7 +2264,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3351,7 +3345,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3400,10 +3394,10 @@
         <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="H4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3426,10 +3420,10 @@
         <v>306</v>
       </c>
       <c r="G5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3452,10 +3446,10 @@
         <v>307</v>
       </c>
       <c r="G6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="H6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3478,10 +3472,10 @@
         <v>308</v>
       </c>
       <c r="G7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3504,10 +3498,10 @@
         <v>309</v>
       </c>
       <c r="G8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="H8" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3530,10 +3524,10 @@
         <v>310</v>
       </c>
       <c r="G9" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H9" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3556,10 +3550,10 @@
         <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H10" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3582,10 +3576,10 @@
         <v>311</v>
       </c>
       <c r="G11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="H11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3608,10 +3602,10 @@
         <v>312</v>
       </c>
       <c r="G12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="H12" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3634,10 +3628,10 @@
         <v>313</v>
       </c>
       <c r="G13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H13" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3660,10 +3654,10 @@
         <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3686,10 +3680,10 @@
         <v>315</v>
       </c>
       <c r="G15" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H15" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3712,10 +3706,10 @@
         <v>316</v>
       </c>
       <c r="G16" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H16" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3738,10 +3732,10 @@
         <v>317</v>
       </c>
       <c r="G17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H17" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3764,10 +3758,10 @@
         <v>318</v>
       </c>
       <c r="G18" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H18" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -3790,10 +3784,10 @@
         <v>319</v>
       </c>
       <c r="G19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H19" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -3816,10 +3810,10 @@
         <v>320</v>
       </c>
       <c r="G20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="H20" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -3842,10 +3836,10 @@
         <v>321</v>
       </c>
       <c r="G21" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H21" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -3868,10 +3862,10 @@
         <v>322</v>
       </c>
       <c r="G22" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="H22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -3894,10 +3888,10 @@
         <v>323</v>
       </c>
       <c r="G23" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -3920,10 +3914,10 @@
         <v>324</v>
       </c>
       <c r="G24" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H24" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -3946,10 +3940,10 @@
         <v>325</v>
       </c>
       <c r="G25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H25" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -3972,10 +3966,10 @@
         <v>326</v>
       </c>
       <c r="G26" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H26" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -3998,10 +3992,10 @@
         <v>327</v>
       </c>
       <c r="G27" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H27" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4024,10 +4018,10 @@
         <v>328</v>
       </c>
       <c r="G28" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H28" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4050,10 +4044,10 @@
         <v>329</v>
       </c>
       <c r="G29" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H29" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4076,10 +4070,10 @@
         <v>330</v>
       </c>
       <c r="G30" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H30" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4102,10 +4096,10 @@
         <v>331</v>
       </c>
       <c r="G31" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H31" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4128,10 +4122,10 @@
         <v>332</v>
       </c>
       <c r="G32" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H32" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -4154,10 +4148,10 @@
         <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H33" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4180,10 +4174,10 @@
         <v>323</v>
       </c>
       <c r="G34" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H34" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4206,10 +4200,10 @@
         <v>333</v>
       </c>
       <c r="G35" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H35" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4232,10 +4226,10 @@
         <v>334</v>
       </c>
       <c r="G36" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H36" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4258,10 +4252,10 @@
         <v>335</v>
       </c>
       <c r="G37" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4284,10 +4278,10 @@
         <v>336</v>
       </c>
       <c r="G38" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H38" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4310,10 +4304,10 @@
         <v>337</v>
       </c>
       <c r="G39" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H39" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4336,10 +4330,10 @@
         <v>338</v>
       </c>
       <c r="G40" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H40" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4362,10 +4356,10 @@
         <v>339</v>
       </c>
       <c r="G41" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H41" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -4388,10 +4382,10 @@
         <v>340</v>
       </c>
       <c r="G42" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H42" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4414,10 +4408,10 @@
         <v>341</v>
       </c>
       <c r="G43" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H43" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4440,10 +4434,10 @@
         <v>342</v>
       </c>
       <c r="G44" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H44" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -4466,10 +4460,10 @@
         <v>343</v>
       </c>
       <c r="G45" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H45" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4492,10 +4486,10 @@
         <v>323</v>
       </c>
       <c r="G46" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H46" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4518,10 +4512,10 @@
         <v>323</v>
       </c>
       <c r="G47" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H47" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4544,10 +4538,10 @@
         <v>344</v>
       </c>
       <c r="G48" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H48" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4570,10 +4564,10 @@
         <v>345</v>
       </c>
       <c r="G49" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H49" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4596,10 +4590,10 @@
         <v>346</v>
       </c>
       <c r="G50" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H50" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4622,10 +4616,10 @@
         <v>347</v>
       </c>
       <c r="G51" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H51" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -4648,10 +4642,10 @@
         <v>348</v>
       </c>
       <c r="G52" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H52" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -4674,10 +4668,10 @@
         <v>349</v>
       </c>
       <c r="G53" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H53" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -4700,10 +4694,10 @@
         <v>350</v>
       </c>
       <c r="G54" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H54" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -4726,10 +4720,10 @@
         <v>351</v>
       </c>
       <c r="G55" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H55" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -4752,10 +4746,10 @@
         <v>352</v>
       </c>
       <c r="G56" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H56" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -4778,10 +4772,10 @@
         <v>353</v>
       </c>
       <c r="G57" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H57" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -4804,10 +4798,10 @@
         <v>354</v>
       </c>
       <c r="G58" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H58" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -4830,10 +4824,10 @@
         <v>355</v>
       </c>
       <c r="G59" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H59" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -4856,10 +4850,10 @@
         <v>356</v>
       </c>
       <c r="G60" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H60" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -4882,10 +4876,10 @@
         <v>357</v>
       </c>
       <c r="G61" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H61" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -4908,10 +4902,10 @@
         <v>358</v>
       </c>
       <c r="G62" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H62" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -4934,10 +4928,10 @@
         <v>359</v>
       </c>
       <c r="G63" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H63" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -4960,10 +4954,10 @@
         <v>360</v>
       </c>
       <c r="G64" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H64" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -4986,10 +4980,10 @@
         <v>361</v>
       </c>
       <c r="G65" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H65" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5012,10 +5006,10 @@
         <v>362</v>
       </c>
       <c r="G66" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H66" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5038,10 +5032,10 @@
         <v>363</v>
       </c>
       <c r="G67" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H67" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5064,10 +5058,10 @@
         <v>364</v>
       </c>
       <c r="G68" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H68" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5087,13 +5081,13 @@
         <v>262</v>
       </c>
       <c r="F69" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G69" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H69" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5113,13 +5107,13 @@
         <v>263</v>
       </c>
       <c r="F70" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G70" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H70" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5139,13 +5133,13 @@
         <v>264</v>
       </c>
       <c r="F71" t="s">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="G71" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="H71" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5168,10 +5162,10 @@
         <v>83</v>
       </c>
       <c r="G72" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H72" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5191,13 +5185,13 @@
         <v>266</v>
       </c>
       <c r="F73" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G73" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="H73" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5217,13 +5211,13 @@
         <v>267</v>
       </c>
       <c r="F74" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G74" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H74" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5243,13 +5237,13 @@
         <v>268</v>
       </c>
       <c r="F75" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G75" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H75" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5269,13 +5263,13 @@
         <v>269</v>
       </c>
       <c r="F76" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G76" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="H76" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5295,13 +5289,13 @@
         <v>270</v>
       </c>
       <c r="F77" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G77" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H77" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5321,13 +5315,13 @@
         <v>271</v>
       </c>
       <c r="F78" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G78" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H78" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5347,13 +5341,13 @@
         <v>272</v>
       </c>
       <c r="F79" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G79" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H79" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -5373,13 +5367,13 @@
         <v>273</v>
       </c>
       <c r="F80" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G80" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H80" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -5399,13 +5393,13 @@
         <v>274</v>
       </c>
       <c r="F81" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G81" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H81" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -5425,13 +5419,13 @@
         <v>275</v>
       </c>
       <c r="F82" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G82" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="H82" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -5451,13 +5445,13 @@
         <v>276</v>
       </c>
       <c r="F83" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G83" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="H83" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -5477,13 +5471,13 @@
         <v>277</v>
       </c>
       <c r="F84" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G84" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H84" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -5503,13 +5497,13 @@
         <v>278</v>
       </c>
       <c r="F85" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="G85" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H85" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -5529,13 +5523,13 @@
         <v>279</v>
       </c>
       <c r="F86" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G86" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="H86" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -5555,13 +5549,13 @@
         <v>280</v>
       </c>
       <c r="F87" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G87" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H87" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -5581,13 +5575,13 @@
         <v>281</v>
       </c>
       <c r="F88" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G88" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H88" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -5607,13 +5601,13 @@
         <v>282</v>
       </c>
       <c r="F89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G89" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="H89" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -5633,13 +5627,13 @@
         <v>283</v>
       </c>
       <c r="F90" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G90" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="H90" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -5659,13 +5653,13 @@
         <v>284</v>
       </c>
       <c r="F91" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G91" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="H91" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -5685,13 +5679,13 @@
         <v>285</v>
       </c>
       <c r="F92" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G92" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H92" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -5711,13 +5705,13 @@
         <v>286</v>
       </c>
       <c r="F93" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G93" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H93" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -5737,13 +5731,13 @@
         <v>287</v>
       </c>
       <c r="F94" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G94" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="H94" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -5763,13 +5757,13 @@
         <v>288</v>
       </c>
       <c r="F95" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G95" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H95" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -5789,13 +5783,13 @@
         <v>289</v>
       </c>
       <c r="F96" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G96" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H96" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -5815,13 +5809,13 @@
         <v>290</v>
       </c>
       <c r="F97" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G97" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H97" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -5841,13 +5835,13 @@
         <v>291</v>
       </c>
       <c r="F98" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G98" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H98" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -5867,13 +5861,13 @@
         <v>292</v>
       </c>
       <c r="F99" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G99" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H99" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -5893,13 +5887,13 @@
         <v>293</v>
       </c>
       <c r="F100" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G100" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H100" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -5919,13 +5913,13 @@
         <v>294</v>
       </c>
       <c r="F101" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G101" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H101" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -5945,13 +5939,13 @@
         <v>295</v>
       </c>
       <c r="F102" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G102" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H102" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -5974,10 +5968,10 @@
         <v>91</v>
       </c>
       <c r="G103" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H103" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -5997,13 +5991,13 @@
         <v>297</v>
       </c>
       <c r="F104" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G104" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H104" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6023,13 +6017,13 @@
         <v>298</v>
       </c>
       <c r="F105" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G105" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H105" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6049,13 +6043,13 @@
         <v>299</v>
       </c>
       <c r="F106" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G106" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H106" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6075,13 +6069,13 @@
         <v>300</v>
       </c>
       <c r="F107" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G107" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H107" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6101,13 +6095,13 @@
         <v>301</v>
       </c>
       <c r="F108" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G108" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H108" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6127,13 +6121,13 @@
         <v>302</v>
       </c>
       <c r="F109" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G109" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H109" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6153,13 +6147,13 @@
         <v>303</v>
       </c>
       <c r="F110" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G110" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H110" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6179,13 +6173,13 @@
         <v>304</v>
       </c>
       <c r="F111" t="s">
-        <v>404</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H111" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
